--- a/outputs/daily/hr_rankings_2026-08-01_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-01_full.xlsx
@@ -4442,34 +4442,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13866,34 +13862,30 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16898,34 +16890,30 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -19134,34 +19122,30 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -21644,28 +21628,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y77" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22750,34 +22738,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -33002,34 +32986,30 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36864,28 +36844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y132" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52040,28 +52024,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W187" t="inlineStr"/>
-      <c r="X187" t="inlineStr"/>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y187" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -79444,34 +79432,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
